--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3F7A9F-35DF-AD45-9C2B-35748E30AC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED63B3E7-99BC-8F43-BE94-A934B7A01DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -1,71 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED63B3E7-99BC-8F43-BE94-A934B7A01DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F88E4A8-5ACD-A047-A98F-790E13F28F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$D$1</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$D$2:$D$10</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$E$2:$E$10</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$F$2:$F$10</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$G$1</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$G$2:$G$10</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$H$1</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$H$2:$H$10</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$I$1</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Sheet1!$I$2:$I$10</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Sheet1!$J$2:$J$10</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Sheet1!$D$10:$J$10</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Sheet1!$D$1:$J$1</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Sheet1!$D$2:$J$2</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Sheet1!$D$3:$J$3</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Sheet1!$D$4:$J$4</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Sheet1!$D$5:$J$5</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Sheet1!$D$6:$J$6</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Sheet1!$D$7:$J$7</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Sheet1!$D$8:$J$8</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Sheet1!$D$9:$J$9</definedName>
-    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$D$1</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$D$2:$D$10</definedName>
-    <definedName name="_xlchart.v2.10" hidden="1">Sheet1!$I$1</definedName>
-    <definedName name="_xlchart.v2.11" hidden="1">Sheet1!$I$2:$I$10</definedName>
-    <definedName name="_xlchart.v2.12" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v2.13" hidden="1">Sheet1!$J$2:$J$10</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$E$2:$E$10</definedName>
-    <definedName name="_xlchart.v2.38" hidden="1">Sheet1!$D$10:$J$10</definedName>
-    <definedName name="_xlchart.v2.39" hidden="1">Sheet1!$D$1:$J$1</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v2.40" hidden="1">Sheet1!$D$2:$J$2</definedName>
-    <definedName name="_xlchart.v2.41" hidden="1">Sheet1!$D$3:$J$3</definedName>
-    <definedName name="_xlchart.v2.42" hidden="1">Sheet1!$D$4:$J$4</definedName>
-    <definedName name="_xlchart.v2.43" hidden="1">Sheet1!$D$5:$J$5</definedName>
-    <definedName name="_xlchart.v2.44" hidden="1">Sheet1!$D$6:$J$6</definedName>
-    <definedName name="_xlchart.v2.45" hidden="1">Sheet1!$D$7:$J$7</definedName>
-    <definedName name="_xlchart.v2.46" hidden="1">Sheet1!$D$8:$J$8</definedName>
-    <definedName name="_xlchart.v2.47" hidden="1">Sheet1!$D$9:$J$9</definedName>
-    <definedName name="_xlchart.v2.5" hidden="1">Sheet1!$F$2:$F$10</definedName>
-    <definedName name="_xlchart.v2.6" hidden="1">Sheet1!$G$1</definedName>
-    <definedName name="_xlchart.v2.7" hidden="1">Sheet1!$G$2:$G$10</definedName>
-    <definedName name="_xlchart.v2.8" hidden="1">Sheet1!$H$1</definedName>
-    <definedName name="_xlchart.v2.9" hidden="1">Sheet1!$H$2:$H$10</definedName>
-  </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -88,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
-    <t>video_id</t>
-  </si>
-  <si>
     <t>Title</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,7 +231,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Hans Zimmer,Interstellar,Movieclips,音楽,共感,Love,Theme song,災害,名作,希望,宇宙,家族,父親,科学,未来,ピアノ,BGM</t>
+    <t>video_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hans Zimmer,Interstellar,Movieclips,音楽,共感,Love,Theme song,災害,名作,希望,宇宙,家族,父親,科学,未来,ピアノ,BGM,宇宙飛行士,宇宙船</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -352,7 +303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -360,9 +311,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -705,43 +653,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2F4CF1-2CF2-B949-9643-07E0C879FE74}">
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="11" max="11" width="113.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -749,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
       </c>
       <c r="D2">
         <v>2.4273738E-2</v>
@@ -776,10 +727,10 @@
         <v>0.68220754699999997</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -787,10 +738,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
       </c>
       <c r="D3">
         <v>6.3761741999999996E-2</v>
@@ -814,10 +765,10 @@
         <v>0.64855390700000004</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -825,10 +776,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
       </c>
       <c r="D4">
         <v>3.3055498000000003E-2</v>
@@ -852,10 +803,10 @@
         <v>0.66408087199999999</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -863,10 +814,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>2.0277915000000001E-2</v>
@@ -889,22 +840,22 @@
       <c r="J5">
         <v>0.67705706700000001</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>24</v>
+      <c r="K5" t="s">
+        <v>23</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>25</v>
+      <c r="B6" t="s">
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>7.3877730000000003E-3</v>
@@ -927,136 +878,136 @@
       <c r="J6">
         <v>0.70919832500000002</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>45</v>
+      <c r="K6" t="s">
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="3" customFormat="1">
-      <c r="A7" s="3">
+    <row r="7" spans="1:12">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>5.4875947000000001E-2</v>
+      </c>
+      <c r="E7">
+        <v>2.3524835000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.6127590000000001E-3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.58529008800000004</v>
+      </c>
+      <c r="I7">
+        <v>0.41286212</v>
+      </c>
+      <c r="J7">
+        <v>0.68198074200000003</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="3">
-        <v>5.4875947000000001E-2</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2.3524835000000001E-2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>2.6127590000000001E-3</v>
-      </c>
-      <c r="G7" s="3">
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>8.5995326999999996E-2</v>
+      </c>
+      <c r="E8">
+        <v>2.0225959000000002E-2</v>
+      </c>
+      <c r="F8">
+        <v>2.5282450000000001E-3</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="H7" s="3">
-        <v>0.58529008800000004</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.41286212</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.68198074200000003</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>29</v>
+      <c r="H8">
+        <v>0.57392178800000004</v>
+      </c>
+      <c r="I8">
+        <v>0.49066356700000002</v>
+      </c>
+      <c r="J8">
+        <v>0.59680386399999996</v>
+      </c>
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="3" customFormat="1">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="3" t="s">
+    <row r="9" spans="1:12">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3">
-        <v>8.5995326999999996E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2.0225959000000002E-2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2.5282450000000001E-3</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9">
+        <v>0.185724941</v>
+      </c>
+      <c r="E9">
+        <v>3.8257547000000003E-2</v>
+      </c>
+      <c r="F9">
+        <v>5.463936E-3</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
-        <v>0.57392178800000004</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0.49066356700000002</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.59680386399999996</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="3" customFormat="1">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="H9">
+        <v>0.59558330100000001</v>
+      </c>
+      <c r="I9">
+        <v>0.41508613</v>
+      </c>
+      <c r="J9">
+        <v>0.56012837900000001</v>
+      </c>
+      <c r="K9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.185724941</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3.8257547000000003E-2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>5.463936E-3</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.59558330100000001</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.41508613</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.56012837900000001</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
       </c>
       <c r="D10">
         <v>0.34394102799999998</v>
@@ -1079,22 +1030,22 @@
       <c r="J10">
         <v>0.534306226</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>43</v>
+      <c r="K10" t="s">
+        <v>42</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
       </c>
       <c r="D11">
         <v>0.34927411800000002</v>
@@ -1117,11 +1068,11 @@
       <c r="J11">
         <v>0.54898409699999995</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" t="s">
         <v>51</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F88E4A8-5ACD-A047-A98F-790E13F28F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8D00BF-3CB8-E340-8BEA-304C851BEF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
@@ -122,10 +122,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sabrina Carpenter,Pop,音楽,MV</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sabrina Carpenter - Espresso</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -150,19 +146,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Gracie Abrams,Pop,音楽,ライブ,共感,癒し</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Olivia Rodrigo,Pop,音楽,MV,レトロ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-La La Land (2016) - Another Day of Sun Scene (1/11) | Movieclips</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://youtu.be/7CVfTd-_qbc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,10 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>La La Land,Movieclips,MV,Pop,音楽,共感,芸術,理想,ダンス,Theme song</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Titanic • My Heart Will Go On • Celine Dion</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,22 +182,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Titanic,Movieclips,MV,Pop,音楽,共感,Love,Theme song,歴史,災害,社会事件,名作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>La La Land,Movieclips,MV,Pop,音楽,共感,理想,ダンス,Love,ピアノ,Theme song,名作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sabrina Carpenter,Pop,音楽,MV,名作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Taylor Swift,Pop,MV,激励,ダンス,名作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Taylor Swift,Pop,MV,Love,名作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -236,6 +207,34 @@
   </si>
   <si>
     <t>Hans Zimmer,Interstellar,Movieclips,音楽,共感,Love,Theme song,災害,名作,希望,宇宙,家族,父親,科学,未来,ピアノ,BGM,宇宙飛行士,宇宙船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>La La Land (2016) - Another Day of Sun Scene (1/11) | Movieclips</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Titanic,Movieclips,MV,Pop,音楽,共感,感動,Love,Theme song,歴史,災害,社会事件,名作,海,船</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sabrina Carpenter,Pop,音楽,MV,名作,海,砂浜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gracie Abrams,Pop,音楽,ライブ,共感,癒し,ギター</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sabrina Carpenter,Pop,音楽,MV,砂漠,road</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>La La Land,Movieclips,MV,Pop,音楽,共感,芸術,理想,ダンス,Theme song,都市,road</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taylor Swift,Pop,MV,激励,ダンス,名作,</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -659,7 +658,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -727,7 +726,7 @@
         <v>0.68220754699999997</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>13</v>
@@ -765,7 +764,7 @@
         <v>0.64855390700000004</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>14</v>
@@ -803,7 +802,7 @@
         <v>0.66408087199999999</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>17</v>
@@ -841,7 +840,7 @@
         <v>0.67705706700000001</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>20</v>
@@ -852,10 +851,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>7.3877730000000003E-3</v>
@@ -879,10 +878,10 @@
         <v>0.70919832500000002</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -890,10 +889,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>5.4875947000000001E-2</v>
@@ -917,10 +916,10 @@
         <v>0.68198074200000003</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -928,10 +927,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>8.5995326999999996E-2</v>
@@ -955,10 +954,10 @@
         <v>0.59680386399999996</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -966,10 +965,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>0.185724941</v>
@@ -993,10 +992,10 @@
         <v>0.56012837900000001</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1004,10 +1003,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D10">
         <v>0.34394102799999998</v>
@@ -1031,10 +1030,10 @@
         <v>0.534306226</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1042,10 +1041,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <v>0.34927411800000002</v>
@@ -1069,10 +1068,10 @@
         <v>0.54898409699999995</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8D00BF-3CB8-E340-8BEA-304C851BEF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5F7A8C-4316-2446-8B52-472D814899F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
@@ -226,15 +226,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sabrina Carpenter,Pop,音楽,MV,砂漠,road</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>La La Land,Movieclips,MV,Pop,音楽,共感,芸術,理想,ダンス,Theme song,都市,road</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Taylor Swift,Pop,MV,激励,ダンス,名作,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sabrina Carpenter,Pop,音楽,MV,砂漠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>La La Land,Movieclips,MV,Pop,音楽,共感,理想,ダンス,Theme song,都市</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -802,7 +802,7 @@
         <v>0.66408087199999999</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>17</v>
@@ -840,7 +840,7 @@
         <v>0.67705706700000001</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>20</v>
@@ -954,7 +954,7 @@
         <v>0.59680386399999996</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>30</v>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5F7A8C-4316-2446-8B52-472D814899F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E93B60-FE2D-BA48-82A2-0EF7FB0FECD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E93B60-FE2D-BA48-82A2-0EF7FB0FECD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A79C33-5127-E043-A901-8830FE0A8D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A79C33-5127-E043-A901-8830FE0A8D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF854341-801D-E143-B637-65289114BD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
@@ -186,10 +186,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Taylor Swift,Pop,MV,Love,名作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hans Zimmer - Interstellar theme song video</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -226,15 +222,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Taylor Swift,Pop,MV,激励,ダンス,名作,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sabrina Carpenter,Pop,音楽,MV,砂漠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>La La Land,Movieclips,MV,Pop,音楽,共感,理想,ダンス,Theme song,都市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taylor Swift,Pop,音楽,MV,Love,名作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taylor Swift,Pop,MV,激励,ダンス,名作,音楽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -658,7 +658,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0.64855390700000004</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>14</v>
@@ -802,7 +802,7 @@
         <v>0.66408087199999999</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>17</v>
@@ -840,7 +840,7 @@
         <v>0.67705706700000001</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>20</v>
@@ -878,7 +878,7 @@
         <v>0.70919832500000002</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>24</v>
@@ -916,7 +916,7 @@
         <v>0.68198074200000003</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>27</v>
@@ -927,7 +927,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
@@ -954,7 +954,7 @@
         <v>0.59680386399999996</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>30</v>
@@ -1030,7 +1030,7 @@
         <v>0.534306226</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>36</v>
@@ -1041,10 +1041,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11">
         <v>0.34927411800000002</v>
@@ -1068,10 +1068,10 @@
         <v>0.54898409699999995</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,13 +8,43 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF854341-801D-E143-B637-65289114BD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28139167-D5EB-E845-9D2D-00E8FFA797BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$D$2:$D$11</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$E$1</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$F$1</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$F$2:$F$11</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$G$1</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$G$2:$G$11</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$H$1</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$H$2:$H$11</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$I$1</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Sheet1!$I$2:$I$11</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Sheet1!$J$1</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Sheet1!$J$2:$J$11</definedName>
+    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$D$2:$D$11</definedName>
+    <definedName name="_xlchart.v2.10" hidden="1">Sheet1!$I$1</definedName>
+    <definedName name="_xlchart.v2.11" hidden="1">Sheet1!$I$2:$I$11</definedName>
+    <definedName name="_xlchart.v2.12" hidden="1">Sheet1!$J$1</definedName>
+    <definedName name="_xlchart.v2.13" hidden="1">Sheet1!$J$2:$J$11</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$E$1</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v2.4" hidden="1">Sheet1!$F$1</definedName>
+    <definedName name="_xlchart.v2.5" hidden="1">Sheet1!$F$2:$F$11</definedName>
+    <definedName name="_xlchart.v2.6" hidden="1">Sheet1!$G$1</definedName>
+    <definedName name="_xlchart.v2.7" hidden="1">Sheet1!$G$2:$G$11</definedName>
+    <definedName name="_xlchart.v2.8" hidden="1">Sheet1!$H$1</definedName>
+    <definedName name="_xlchart.v2.9" hidden="1">Sheet1!$H$2:$H$11</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28139167-D5EB-E845-9D2D-00E8FFA797BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE8F7A4-CA90-0148-94FD-2A680B445964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
@@ -16,34 +16,34 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet1!$D$1</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet1!$D$2:$D$11</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet1!$E$2:$E$11</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet1!$F$2:$F$11</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet1!$G$1</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Sheet1!$G$2:$G$11</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Sheet1!$H$1</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Sheet1!$H$2:$H$11</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Sheet1!$I$1</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Sheet1!$I$2:$I$11</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Sheet1!$J$2:$J$11</definedName>
-    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$D$1</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$D$2:$D$11</definedName>
-    <definedName name="_xlchart.v2.10" hidden="1">Sheet1!$I$1</definedName>
-    <definedName name="_xlchart.v2.11" hidden="1">Sheet1!$I$2:$I$11</definedName>
-    <definedName name="_xlchart.v2.12" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v2.13" hidden="1">Sheet1!$J$2:$J$11</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Sheet1!$E$1</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Sheet1!$E$2:$E$11</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">Sheet1!$F$1</definedName>
-    <definedName name="_xlchart.v2.5" hidden="1">Sheet1!$F$2:$F$11</definedName>
-    <definedName name="_xlchart.v2.6" hidden="1">Sheet1!$G$1</definedName>
-    <definedName name="_xlchart.v2.7" hidden="1">Sheet1!$G$2:$G$11</definedName>
-    <definedName name="_xlchart.v2.8" hidden="1">Sheet1!$H$1</definedName>
-    <definedName name="_xlchart.v2.9" hidden="1">Sheet1!$H$2:$H$11</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$D$2:$D$11</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Sheet1!$I$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Sheet1!$I$2:$I$11</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Sheet1!$J$1</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Sheet1!$J$2:$J$11</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$E$1</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$F$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$F$2:$F$11</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$G$1</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$G$2:$G$11</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$H$1</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$H$2:$H$11</definedName>
+    <definedName name="_xlchart.v2.14" hidden="1">Sheet1!$D$1</definedName>
+    <definedName name="_xlchart.v2.15" hidden="1">Sheet1!$D$2:$D$11</definedName>
+    <definedName name="_xlchart.v2.16" hidden="1">Sheet1!$E$1</definedName>
+    <definedName name="_xlchart.v2.17" hidden="1">Sheet1!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v2.18" hidden="1">Sheet1!$F$1</definedName>
+    <definedName name="_xlchart.v2.19" hidden="1">Sheet1!$F$2:$F$11</definedName>
+    <definedName name="_xlchart.v2.20" hidden="1">Sheet1!$G$1</definedName>
+    <definedName name="_xlchart.v2.21" hidden="1">Sheet1!$G$2:$G$11</definedName>
+    <definedName name="_xlchart.v2.22" hidden="1">Sheet1!$H$1</definedName>
+    <definedName name="_xlchart.v2.23" hidden="1">Sheet1!$H$2:$H$11</definedName>
+    <definedName name="_xlchart.v2.24" hidden="1">Sheet1!$I$1</definedName>
+    <definedName name="_xlchart.v2.25" hidden="1">Sheet1!$I$2:$I$11</definedName>
+    <definedName name="_xlchart.v2.26" hidden="1">Sheet1!$J$1</definedName>
+    <definedName name="_xlchart.v2.27" hidden="1">Sheet1!$J$2:$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -361,6 +361,1324 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>悲しい</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.4273738E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.3761741999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3055498000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0277915000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.3877730000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4875947000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5995326999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.185724941</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.34394102799999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.34927411800000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FB5F-6E46-BE1F-2EF412A937D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>不安</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.0787217E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9402658E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3773123999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5208436000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.9251820000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3524835000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0225959000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.8257547000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4505192000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.9908303000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FB5F-6E46-BE1F-2EF412A937D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>怒り</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5450450000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2648740000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0138957000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4625910000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6127590000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5282450000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.463936E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.1395419999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.5453669999999998E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FB5F-6E46-BE1F-2EF412A937D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>嫌悪</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.6968040000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7725219999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5099160000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.069479E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.0697709999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.7726840000000001E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-FB5F-6E46-BE1F-2EF412A937D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>信頼</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$2:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.54752161200000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.58477075300000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56749059400000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55257837200000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.54443593300000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58529008800000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.57392178800000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.59558330100000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.62949398099999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.61547381499999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-FB5F-6E46-BE1F-2EF412A937D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>驚き</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.46365633299999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45184532700000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.490177635</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48666996000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.46542130599999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.41286212</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.49066356700000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.41508613</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.423675988</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.40757758999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-FB5F-6E46-BE1F-2EF412A937D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>嬉しい</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$2:$J$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.68220754699999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64855390700000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66408087199999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.67705706700000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.70919832500000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.68198074200000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.59680386399999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.56012837900000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.534306226</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.54898409699999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-FB5F-6E46-BE1F-2EF412A937D9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="868315392"/>
+        <c:axId val="868318080"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="868315392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="868318080"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="868318080"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="868315392"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>3009900</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E40C689A-05C3-A8C4-7995-6D69DBF27628}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1119,5 +2437,6 @@
     <hyperlink ref="L11" r:id="rId10" xr:uid="{D9B846D2-EAFA-CE44-9E7B-8126A883B4CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9FF44D-B167-1745-BFDB-ED82C431D1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B9C09-4868-B044-ABFE-121E0ACB27D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12720" yWindow="0" windowWidth="16080" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,6 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$D$11:$J$11</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$D$1:$J$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$D$11:$J$11</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$D$1:$J$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -342,6 +336,1732 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="filled"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$1:$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>悲しい</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>不安</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>怒り</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>嫌悪</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>信頼</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>驚き</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>嬉しい</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$11:$J$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.34927411800000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.9908303000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5453669999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.7726840000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.61547381499999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.40757758999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54898409699999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-334E-DA45-B9DC-2B4B1C4644A5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="50196"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Sheet1!$D$1:$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>悲しい</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>不安</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>怒り</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>嫌悪</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>信頼</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>驚き</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>嬉しい</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Sheet1!$D$100:$J$100</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.40824829000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27216552700000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.40824829000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.54433105400000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54433105400000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-334E-DA45-B9DC-2B4B1C4644A5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="866005696"/>
+        <c:axId val="866005248"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="866005696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="866005248"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="866005248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="866005696"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>悲しい</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.4273738E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.3761741999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.3055498000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.0277915000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.3877730000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4875947000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5995326999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.185724941</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.34394102799999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.34927411800000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4DA1-D547-93E1-BB272A31B78C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>不安</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.0787217E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9402658E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3773123999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5208436000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.9251820000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3524835000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0225959000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.8257547000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.4505192000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.9908303000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4DA1-D547-93E1-BB272A31B78C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>怒り</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5450450000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2648740000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.0138957000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4625910000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6127590000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5282450000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.463936E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.1395419999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.5453669999999998E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4DA1-D547-93E1-BB272A31B78C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>嫌悪</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>2.6968040000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7725219999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5099160000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.069479E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.0697709999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.7726840000000001E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4DA1-D547-93E1-BB272A31B78C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>信頼</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$H$2:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.54752161200000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.58477075300000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.56749059400000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55257837200000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.54443593300000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58529008800000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.57392178800000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.59558330100000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.62949398099999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.61547381499999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4DA1-D547-93E1-BB272A31B78C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>驚き</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$2:$I$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.46365633299999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45184532700000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.490177635</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48666996000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.46542130599999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.41286212</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.49066356700000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.41508613</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.423675988</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.40757758999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-4DA1-D547-93E1-BB272A31B78C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>嬉しい</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$J$2:$J$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.68220754699999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.64855390700000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66408087199999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.67705706700000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.70919832500000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.68198074200000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.59680386399999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.56012837900000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.534306226</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.54898409699999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-4DA1-D547-93E1-BB272A31B78C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="866496768"/>
+        <c:axId val="866498560"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="866496768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="866498560"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="866498560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="866496768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>308206</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>161692</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>61950</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>139390</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="图表 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98E2B896-7F87-1163-E27C-47FB642088C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>106866</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>146204</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>4259146</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>123901</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="图表 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6861C13C-8B00-28EA-85BC-A1ED907B205A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -397,6 +2117,29 @@
           </cell>
           <cell r="J80">
             <v>0.141421356</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="D100">
+            <v>0.40824829000000001</v>
+          </cell>
+          <cell r="E100">
+            <v>0.27216552700000002</v>
+          </cell>
+          <cell r="F100">
+            <v>0</v>
+          </cell>
+          <cell r="G100">
+            <v>0</v>
+          </cell>
+          <cell r="H100">
+            <v>0.40824829000000001</v>
+          </cell>
+          <cell r="I100">
+            <v>0.54433105400000004</v>
+          </cell>
+          <cell r="J100">
+            <v>0.54433105400000004</v>
           </cell>
         </row>
       </sheetData>
@@ -1161,5 +2904,6 @@
     <hyperlink ref="L11" r:id="rId10" xr:uid="{D9B846D2-EAFA-CE44-9E7B-8126A883B4CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B9C09-4868-B044-ABFE-121E0ACB27D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0E9000-07CF-CE49-A7C1-1A54F856EA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2094,29 +2094,6 @@
           </cell>
           <cell r="J1" t="str">
             <v>嬉しい</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="D80">
-            <v>0.56568542499999996</v>
-          </cell>
-          <cell r="E80">
-            <v>0.282842712</v>
-          </cell>
-          <cell r="F80">
-            <v>0.56568542499999996</v>
-          </cell>
-          <cell r="G80">
-            <v>0.282842712</v>
-          </cell>
-          <cell r="H80">
-            <v>0</v>
-          </cell>
-          <cell r="I80">
-            <v>0.42426406900000002</v>
-          </cell>
-          <cell r="J80">
-            <v>0.141421356</v>
           </cell>
         </row>
         <row r="100">

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0E9000-07CF-CE49-A7C1-1A54F856EA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3416B16-618B-FB41-93C8-5FE83C0FBFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3416B16-618B-FB41-93C8-5FE83C0FBFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA969F0-E747-264E-9150-22A2427D8B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>

--- a/videos_1.xlsx
+++ b/videos_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA969F0-E747-264E-9150-22A2427D8B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A96D4C3-485C-BA4D-A0FD-183F8B14E865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{E782D53B-1D4F-CD45-BA20-5FA0010CCCB3}"/>
   </bookViews>
